--- a/data/trans_orig/P5703-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5703-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2007</t>
+          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>270455</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>320008</t>
+          <t>319603</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>238173</t>
+          <t>238372</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>286959</t>
+          <t>288299</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>520500</t>
+          <t>523299</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>597162</t>
+          <t>594335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197692</t>
+          <t>197355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246002</t>
+          <t>244492</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203970</t>
+          <t>201772</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250666</t>
+          <t>250659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>415247</t>
+          <t>417164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>482786</t>
+          <t>485537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132289</t>
+          <t>132083</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>176017</t>
+          <t>175467</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126486</t>
+          <t>127017</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>172104</t>
+          <t>170074</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>275908</t>
+          <t>272675</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>336166</t>
+          <t>330375</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35612</t>
+          <t>35243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28005</t>
+          <t>28559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51298</t>
+          <t>52791</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48597</t>
+          <t>47616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78741</t>
+          <t>79222</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>20564</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21539</t>
+          <t>21754</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>419290</t>
+          <t>421089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>482768</t>
+          <t>484809</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>395084</t>
+          <t>397497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>461362</t>
+          <t>462087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>837900</t>
+          <t>837207</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>923271</t>
+          <t>925226</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>252132</t>
+          <t>251100</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308699</t>
+          <t>309587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224957</t>
+          <t>221727</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>281017</t>
+          <t>277532</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>494097</t>
+          <t>488722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>568651</t>
+          <t>569821</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136960</t>
+          <t>136103</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>184241</t>
+          <t>181382</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148215</t>
+          <t>148263</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>198435</t>
+          <t>196121</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>299477</t>
+          <t>299508</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>366339</t>
+          <t>365913</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47163</t>
+          <t>46348</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79174</t>
+          <t>77462</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80321</t>
+          <t>78951</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117888</t>
+          <t>117606</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134079</t>
+          <t>137829</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>185361</t>
+          <t>186800</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>19785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11590</t>
+          <t>11312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>29392</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19975</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42773</t>
+          <t>42804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>303166</t>
+          <t>302639</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>356196</t>
+          <t>353913</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>301857</t>
+          <t>304189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>351585</t>
+          <t>354987</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>622064</t>
+          <t>620670</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>696710</t>
+          <t>695317</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,1%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161981</t>
+          <t>164324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208242</t>
+          <t>213270</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138499</t>
+          <t>137784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179659</t>
+          <t>182383</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>309261</t>
+          <t>312243</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375871</t>
+          <t>374818</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82869</t>
+          <t>82483</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120065</t>
+          <t>120132</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>117641</t>
+          <t>116569</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158825</t>
+          <t>159784</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>209751</t>
+          <t>209620</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>264132</t>
+          <t>266340</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38830</t>
+          <t>40281</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69328</t>
+          <t>69582</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39050</t>
+          <t>38593</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67454</t>
+          <t>65595</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86312</t>
+          <t>86013</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127509</t>
+          <t>126360</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29929</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>418624</t>
+          <t>418892</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>479110</t>
+          <t>481372</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>467094</t>
+          <t>469631</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>529016</t>
+          <t>531686</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>904738</t>
+          <t>908989</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>995597</t>
+          <t>999482</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,48%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>211980</t>
+          <t>211642</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>263381</t>
+          <t>262923</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>218402</t>
+          <t>217751</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>271127</t>
+          <t>272309</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>441626</t>
+          <t>445997</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>518105</t>
+          <t>519193</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>153104</t>
+          <t>151277</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>197778</t>
+          <t>200122</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>147761</t>
+          <t>144471</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>198143</t>
+          <t>195647</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>311355</t>
+          <t>310669</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>380182</t>
+          <t>375383</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51952</t>
+          <t>50795</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>83194</t>
+          <t>81774</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>81962</t>
+          <t>82960</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>121549</t>
+          <t>120517</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>142627</t>
+          <t>143754</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192294</t>
+          <t>192623</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25610</t>
+          <t>26761</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>17040</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37085</t>
+          <t>36921</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>28995</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54390</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1469700</t>
+          <t>1468697</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1581797</t>
+          <t>1590158</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1464941</t>
+          <t>1466606</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1578238</t>
+          <t>1580649</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2963721</t>
+          <t>2969696</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3127454</t>
+          <t>3123921</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,95%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>874147</t>
+          <t>871841</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>976032</t>
+          <t>978258</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>832271</t>
+          <t>832167</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>931112</t>
+          <t>931160</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1726980</t>
+          <t>1729773</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1869982</t>
+          <t>1872562</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>544797</t>
+          <t>543153</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>631452</t>
+          <t>626235</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>580551</t>
+          <t>580445</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>672868</t>
+          <t>670218</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1156129</t>
+          <t>1149590</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1282603</t>
+          <t>1278501</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>173807</t>
+          <t>174680</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>232141</t>
+          <t>232339</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>259061</t>
+          <t>255708</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>322382</t>
+          <t>323884</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>449361</t>
+          <t>449547</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>534974</t>
+          <t>537570</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>25258</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>50927</t>
+          <t>50635</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>50610</t>
+          <t>49099</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>83052</t>
+          <t>81215</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>81270</t>
+          <t>80620</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>121550</t>
+          <t>122136</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2012</t>
+          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>334541</t>
+          <t>337147</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>385486</t>
+          <t>387053</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>288317</t>
+          <t>291063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>342354</t>
+          <t>343048</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>637957</t>
+          <t>638380</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>715122</t>
+          <t>716652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165392</t>
+          <t>165645</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213685</t>
+          <t>215849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>194781</t>
+          <t>194707</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245322</t>
+          <t>245604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>373768</t>
+          <t>369602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>442341</t>
+          <t>443566</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98130</t>
+          <t>97457</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>137266</t>
+          <t>138091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>84193</t>
+          <t>81165</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>121030</t>
+          <t>120902</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>190574</t>
+          <t>189918</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>246909</t>
+          <t>246258</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40235</t>
+          <t>39532</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28983</t>
+          <t>28798</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54187</t>
+          <t>53192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52470</t>
+          <t>54028</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85972</t>
+          <t>86434</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15911</t>
+          <t>15770</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30174</t>
+          <t>31104</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40043</t>
+          <t>39749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>444256</t>
+          <t>444414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>511575</t>
+          <t>509492</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>398086</t>
+          <t>395771</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>463307</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>862077</t>
+          <t>863596</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>955666</t>
+          <t>954528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,65%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>247877</t>
+          <t>250201</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309429</t>
+          <t>309483</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>289922</t>
+          <t>290905</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>351051</t>
+          <t>354898</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>562615</t>
+          <t>559999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>645179</t>
+          <t>644133</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>174902</t>
+          <t>173494</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>226684</t>
+          <t>227000</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182419</t>
+          <t>182145</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>234346</t>
+          <t>238159</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>372880</t>
+          <t>373814</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>451037</t>
+          <t>448946</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36550</t>
+          <t>36225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66444</t>
+          <t>65901</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40676</t>
+          <t>42704</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70892</t>
+          <t>72721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85285</t>
+          <t>84501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127008</t>
+          <t>127307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18210</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25138</t>
+          <t>24167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>15914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36887</t>
+          <t>36115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>328573</t>
+          <t>328304</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>385038</t>
+          <t>388626</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>331044</t>
+          <t>329766</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>387317</t>
+          <t>385399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>677482</t>
+          <t>675836</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>756964</t>
+          <t>754904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160850</t>
+          <t>161274</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211567</t>
+          <t>212547</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180215</t>
+          <t>178750</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>231235</t>
+          <t>232345</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354736</t>
+          <t>355533</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425813</t>
+          <t>424611</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>131392</t>
+          <t>130919</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180039</t>
+          <t>180010</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>127109</t>
+          <t>125212</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>173010</t>
+          <t>172993</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>271009</t>
+          <t>268462</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>338053</t>
+          <t>336176</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29574</t>
+          <t>27882</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>53861</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33458</t>
+          <t>33928</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62297</t>
+          <t>61358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68289</t>
+          <t>68999</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108962</t>
+          <t>106939</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26732</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12798</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>31188</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24092</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49665</t>
+          <t>50038</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>389436</t>
+          <t>385489</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>451289</t>
+          <t>449206</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>391121</t>
+          <t>394434</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>458022</t>
+          <t>459692</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>802803</t>
+          <t>800587</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>889329</t>
+          <t>887552</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>295805</t>
+          <t>294851</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>355459</t>
+          <t>356505</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>321209</t>
+          <t>321913</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>385212</t>
+          <t>386483</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>634718</t>
+          <t>642636</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>720115</t>
+          <t>727649</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121088</t>
+          <t>121449</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>167659</t>
+          <t>168175</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>161256</t>
+          <t>161599</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>210891</t>
+          <t>211413</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>297126</t>
+          <t>295080</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>366074</t>
+          <t>359790</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29390</t>
+          <t>30286</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54459</t>
+          <t>55630</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29904</t>
+          <t>31853</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58308</t>
+          <t>58770</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68743</t>
+          <t>68088</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>104848</t>
+          <t>105817</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26400</t>
+          <t>25483</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23571</t>
+          <t>24178</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47682</t>
+          <t>48431</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36405</t>
+          <t>37392</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>65636</t>
+          <t>65699</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1560316</t>
+          <t>1559329</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1675107</t>
+          <t>1683584</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1471190</t>
+          <t>1472178</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1588902</t>
+          <t>1587016</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3061652</t>
+          <t>3052310</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3236546</t>
+          <t>3230096</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>924073</t>
+          <t>928383</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1036707</t>
+          <t>1032602</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1045045</t>
+          <t>1043843</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1154267</t>
+          <t>1154173</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1991003</t>
+          <t>1990345</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2154523</t>
+          <t>2154909</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>573557</t>
+          <t>567785</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>665343</t>
+          <t>662600</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>599451</t>
+          <t>595507</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>693070</t>
+          <t>688294</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1192398</t>
+          <t>1192255</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1328473</t>
+          <t>1319142</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>133787</t>
+          <t>134760</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>187098</t>
+          <t>185508</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>157561</t>
+          <t>158204</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>212600</t>
+          <t>212346</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>306607</t>
+          <t>306220</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>383538</t>
+          <t>380875</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32833</t>
+          <t>33574</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>63701</t>
+          <t>63718</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>71929</t>
+          <t>72091</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>109745</t>
+          <t>110997</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>113785</t>
+          <t>113099</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>161961</t>
+          <t>164374</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2016</t>
+          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2016 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>276138</t>
+          <t>275442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>327968</t>
+          <t>329729</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>228668</t>
+          <t>230234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>278708</t>
+          <t>278761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>517829</t>
+          <t>519732</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>593799</t>
+          <t>590675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,96%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>150955</t>
+          <t>151422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>194530</t>
+          <t>196974</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185787</t>
+          <t>185017</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>233403</t>
+          <t>234585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>350734</t>
+          <t>350137</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415619</t>
+          <t>415157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112702</t>
+          <t>115143</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156935</t>
+          <t>158769</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>117149</t>
+          <t>113980</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156368</t>
+          <t>156113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>242570</t>
+          <t>240586</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>299970</t>
+          <t>302638</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40095</t>
+          <t>40117</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69948</t>
+          <t>68221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42490</t>
+          <t>40558</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70553</t>
+          <t>68831</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88247</t>
+          <t>89181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127841</t>
+          <t>130678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17971</t>
+          <t>19536</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10755</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20231</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>415247</t>
+          <t>412802</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>480284</t>
+          <t>481510</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>394838</t>
+          <t>397829</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>462226</t>
+          <t>464155</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>834113</t>
+          <t>830768</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>925779</t>
+          <t>925298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>254222</t>
+          <t>253040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311137</t>
+          <t>311472</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>257804</t>
+          <t>256150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316923</t>
+          <t>318666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>528906</t>
+          <t>527624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>613129</t>
+          <t>610711</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>181870</t>
+          <t>185185</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>237866</t>
+          <t>237715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>196752</t>
+          <t>198132</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>251534</t>
+          <t>251139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>396056</t>
+          <t>394293</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>468419</t>
+          <t>470114</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43401</t>
+          <t>44534</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74097</t>
+          <t>75419</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63296</t>
+          <t>63730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99947</t>
+          <t>98794</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117133</t>
+          <t>115979</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162219</t>
+          <t>164117</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>15520</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36598</t>
+          <t>36725</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13827</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33594</t>
+          <t>34264</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34320</t>
+          <t>33592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62215</t>
+          <t>62449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>233159</t>
+          <t>232191</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>283197</t>
+          <t>285953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>248645</t>
+          <t>251281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>303644</t>
+          <t>306324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>498808</t>
+          <t>498972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>574336</t>
+          <t>570682</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202541</t>
+          <t>203508</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>252190</t>
+          <t>256408</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195933</t>
+          <t>198024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250234</t>
+          <t>249593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>416415</t>
+          <t>417979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>486499</t>
+          <t>489494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,83%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>175734</t>
+          <t>177818</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>224384</t>
+          <t>227221</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>170068</t>
+          <t>169561</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>221137</t>
+          <t>220835</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>360856</t>
+          <t>361269</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>432121</t>
+          <t>431069</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31201</t>
+          <t>30480</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56453</t>
+          <t>56746</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50571</t>
+          <t>50746</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83226</t>
+          <t>82713</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89783</t>
+          <t>89283</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>129498</t>
+          <t>130454</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37933</t>
+          <t>37106</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30424</t>
+          <t>30148</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32296</t>
+          <t>34378</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60715</t>
+          <t>62767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>372784</t>
+          <t>372439</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>432511</t>
+          <t>433256</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>432579</t>
+          <t>434300</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>502926</t>
+          <t>502218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>829681</t>
+          <t>826466</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>918367</t>
+          <t>919162</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>256314</t>
+          <t>255912</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>315635</t>
+          <t>315307</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>285932</t>
+          <t>285701</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>348367</t>
+          <t>351631</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>562801</t>
+          <t>562484</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>644517</t>
+          <t>641804</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>152097</t>
+          <t>153323</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>198893</t>
+          <t>199929</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>142976</t>
+          <t>139660</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>193833</t>
+          <t>190751</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>310418</t>
+          <t>306269</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>381921</t>
+          <t>378429</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>72181</t>
+          <t>71029</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53264</t>
+          <t>52645</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87889</t>
+          <t>87483</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102228</t>
+          <t>102557</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>147636</t>
+          <t>146377</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22855</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14905</t>
+          <t>14707</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36537</t>
+          <t>35433</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25644</t>
+          <t>25484</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50875</t>
+          <t>51638</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1347480</t>
+          <t>1349411</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1465269</t>
+          <t>1470011</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1369782</t>
+          <t>1374481</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1486422</t>
+          <t>1494620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2763856</t>
+          <t>2757405</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2918950</t>
+          <t>2917580</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>921177</t>
+          <t>916647</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1025065</t>
+          <t>1023124</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>981288</t>
+          <t>975117</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1084752</t>
+          <t>1086022</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1925052</t>
+          <t>1927644</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2080494</t>
+          <t>2089242</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,19%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>671368</t>
+          <t>670098</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>769840</t>
+          <t>766896</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>673649</t>
+          <t>672026</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>771566</t>
+          <t>773456</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1371033</t>
+          <t>1373793</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1507734</t>
+          <t>1507132</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>179812</t>
+          <t>183791</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>241424</t>
+          <t>240852</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>238326</t>
+          <t>236983</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>306528</t>
+          <t>300976</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>433444</t>
+          <t>437149</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>519130</t>
+          <t>523237</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>57604</t>
+          <t>58716</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>91917</t>
+          <t>91583</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>66098</t>
+          <t>67172</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>104437</t>
+          <t>105556</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>134917</t>
+          <t>133624</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>187045</t>
+          <t>186605</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2023</t>
+          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2023 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>338375</t>
+          <t>338602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>391641</t>
+          <t>390445</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>329773</t>
+          <t>329027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>368912</t>
+          <t>370274</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>683422</t>
+          <t>680233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>750955</t>
+          <t>747759</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>142024</t>
+          <t>139311</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185560</t>
+          <t>183419</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>176807</t>
+          <t>177805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>214788</t>
+          <t>212843</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>327277</t>
+          <t>327420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>384267</t>
+          <t>386261</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53943</t>
+          <t>55481</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85149</t>
+          <t>85299</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78623</t>
+          <t>78342</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>105350</t>
+          <t>103760</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>139907</t>
+          <t>140345</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>179599</t>
+          <t>180866</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15380</t>
+          <t>15090</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34114</t>
+          <t>32284</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20802</t>
+          <t>19944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>35446</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39640</t>
+          <t>39614</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62082</t>
+          <t>60527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22296</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>15283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32450</t>
+          <t>32036</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>596122</t>
+          <t>598990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>930142</t>
+          <t>927839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>426166</t>
+          <t>426126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>480009</t>
+          <t>479069</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1044681</t>
+          <t>1043072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1487247</t>
+          <t>1504441</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>70,28%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167128</t>
+          <t>153328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>396330</t>
+          <t>392146</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>287691</t>
+          <t>287545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336084</t>
+          <t>335472</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>420540</t>
+          <t>401594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>704091</t>
+          <t>707056</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51483</t>
+          <t>48345</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126094</t>
+          <t>126138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99003</t>
+          <t>100011</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>129701</t>
+          <t>131125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>141033</t>
+          <t>135610</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>245082</t>
+          <t>246603</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20143</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64241</t>
+          <t>64478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44218</t>
+          <t>45324</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72103</t>
+          <t>71615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68043</t>
+          <t>68586</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124122</t>
+          <t>125662</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26467</t>
+          <t>26486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>12930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26996</t>
+          <t>26747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23012</t>
+          <t>23465</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46234</t>
+          <t>47336</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>315177</t>
+          <t>318949</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>378577</t>
+          <t>381865</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>175167</t>
+          <t>188844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>481988</t>
+          <t>481038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409641</t>
+          <t>461102</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>835079</t>
+          <t>837246</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>214276</t>
+          <t>210408</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>272877</t>
+          <t>270993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>286840</t>
+          <t>289976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>672314</t>
+          <t>670626</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>524695</t>
+          <t>524351</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1058390</t>
+          <t>1030766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>63,03%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64834</t>
+          <t>63660</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102936</t>
+          <t>101737</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44653</t>
+          <t>42707</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>115257</t>
+          <t>116519</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>106276</t>
+          <t>104426</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>199857</t>
+          <t>201570</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13445</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32109</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16627</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49067</t>
+          <t>48892</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36059</t>
+          <t>35215</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71763</t>
+          <t>69455</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23787</t>
+          <t>24362</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18704</t>
+          <t>17990</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15268</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>37130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>439209</t>
+          <t>437071</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>503787</t>
+          <t>502919</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>534820</t>
+          <t>532961</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>679409</t>
+          <t>684699</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>994229</t>
+          <t>994736</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1160861</t>
+          <t>1165806</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,88%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>231044</t>
+          <t>232991</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>287102</t>
+          <t>288377</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>221969</t>
+          <t>224604</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>309814</t>
+          <t>310170</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>476630</t>
+          <t>472672</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>577205</t>
+          <t>579247</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99454</t>
+          <t>99861</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>142854</t>
+          <t>141188</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>107580</t>
+          <t>105083</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155848</t>
+          <t>156331</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>221628</t>
+          <t>218915</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>287375</t>
+          <t>284529</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37067</t>
+          <t>37302</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64392</t>
+          <t>65427</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56035</t>
+          <t>56218</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88223</t>
+          <t>88457</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>103023</t>
+          <t>102465</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>142861</t>
+          <t>143014</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>20018</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39303</t>
+          <t>39974</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>19522</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34418</t>
+          <t>35326</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43009</t>
+          <t>42174</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>71389</t>
+          <t>69352</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1772160</t>
+          <t>1777086</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2243699</t>
+          <t>2238237</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1419020</t>
+          <t>1343495</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1886824</t>
+          <t>1882755</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3367631</t>
+          <t>3378310</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4027066</t>
+          <t>3989599</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,23%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>755576</t>
+          <t>761979</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1060888</t>
+          <t>1057465</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1056860</t>
+          <t>1060302</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1699449</t>
+          <t>1822493</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1956465</t>
+          <t>1988893</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2650122</t>
+          <t>2621105</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>277734</t>
+          <t>289046</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>410980</t>
+          <t>410964</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>340531</t>
+          <t>339331</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>466625</t>
+          <t>465736</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>684332</t>
+          <t>666341</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>852338</t>
+          <t>859817</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>104043</t>
+          <t>104626</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>164592</t>
+          <t>165982</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>153552</t>
+          <t>150533</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>217593</t>
+          <t>218401</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>276934</t>
+          <t>280962</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>365805</t>
+          <t>365605</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>51734</t>
+          <t>53845</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>91994</t>
+          <t>91305</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>50950</t>
+          <t>52190</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>79551</t>
+          <t>79589</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>113459</t>
+          <t>115044</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>161149</t>
+          <t>161177</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">

--- a/data/trans_orig/P5703-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5703-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>266385</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>319603</t>
+          <t>318451</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>238372</t>
+          <t>239423</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>288299</t>
+          <t>288561</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>523299</t>
+          <t>519426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>594335</t>
+          <t>591571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197355</t>
+          <t>200116</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244492</t>
+          <t>248470</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>201772</t>
+          <t>204391</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250659</t>
+          <t>252529</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>417164</t>
+          <t>413354</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>485537</t>
+          <t>482450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132083</t>
+          <t>131522</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>175467</t>
+          <t>174578</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>127017</t>
+          <t>128271</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170074</t>
+          <t>169401</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>272675</t>
+          <t>274198</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>330375</t>
+          <t>331839</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35243</t>
+          <t>36869</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28559</t>
+          <t>28214</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52791</t>
+          <t>51234</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47616</t>
+          <t>48315</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79222</t>
+          <t>79307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20564</t>
+          <t>19529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21754</t>
+          <t>21234</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>421089</t>
+          <t>421002</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>484809</t>
+          <t>484593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>397497</t>
+          <t>395543</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>462087</t>
+          <t>459453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>837207</t>
+          <t>833529</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>925226</t>
+          <t>929306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,15%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>251100</t>
+          <t>249558</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309587</t>
+          <t>308679</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>221727</t>
+          <t>224849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277532</t>
+          <t>278677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>488722</t>
+          <t>490729</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>569821</t>
+          <t>571446</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136103</t>
+          <t>137694</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>181382</t>
+          <t>184132</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148263</t>
+          <t>147573</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>196121</t>
+          <t>198624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>299508</t>
+          <t>297552</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>365913</t>
+          <t>367051</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46348</t>
+          <t>45840</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77462</t>
+          <t>78011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78951</t>
+          <t>79502</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117606</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137829</t>
+          <t>134265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>186800</t>
+          <t>183523</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>20574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29392</t>
+          <t>29910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19824</t>
+          <t>19985</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42804</t>
+          <t>42474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>302639</t>
+          <t>302401</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>353913</t>
+          <t>357250</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>304189</t>
+          <t>302401</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>354987</t>
+          <t>351090</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>620670</t>
+          <t>623318</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>695317</t>
+          <t>696960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164324</t>
+          <t>159809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>213270</t>
+          <t>209970</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137784</t>
+          <t>136797</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>182383</t>
+          <t>179422</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>312243</t>
+          <t>310916</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>374818</t>
+          <t>376974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82483</t>
+          <t>79993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120132</t>
+          <t>119875</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>116569</t>
+          <t>114416</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159784</t>
+          <t>156809</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>209620</t>
+          <t>210346</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>266340</t>
+          <t>267858</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40281</t>
+          <t>38392</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69582</t>
+          <t>67716</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38593</t>
+          <t>38531</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65595</t>
+          <t>66453</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86013</t>
+          <t>86588</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126360</t>
+          <t>126270</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17780</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>418892</t>
+          <t>420046</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>481372</t>
+          <t>480525</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>469631</t>
+          <t>467447</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>531686</t>
+          <t>531856</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>908989</t>
+          <t>904086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>999482</t>
+          <t>992747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,14%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>211642</t>
+          <t>213628</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>262923</t>
+          <t>263289</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>217751</t>
+          <t>218670</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>272309</t>
+          <t>271589</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>445997</t>
+          <t>443103</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>519193</t>
+          <t>520313</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>151277</t>
+          <t>154263</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>200122</t>
+          <t>200814</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>144471</t>
+          <t>146821</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>195647</t>
+          <t>196669</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>310669</t>
+          <t>310999</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>375383</t>
+          <t>378544</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50795</t>
+          <t>49728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81774</t>
+          <t>79428</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>82960</t>
+          <t>83823</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>120517</t>
+          <t>124230</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>143754</t>
+          <t>143459</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192623</t>
+          <t>193681</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26761</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17040</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36921</t>
+          <t>35610</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28995</t>
+          <t>28900</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54112</t>
+          <t>56118</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1468697</t>
+          <t>1471327</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1590158</t>
+          <t>1582269</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1466606</t>
+          <t>1464020</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1580649</t>
+          <t>1570678</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2969696</t>
+          <t>2965820</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3123921</t>
+          <t>3126318</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,99%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>871841</t>
+          <t>869193</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>978258</t>
+          <t>974464</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>832167</t>
+          <t>829133</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>931160</t>
+          <t>932385</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1729773</t>
+          <t>1728190</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1872562</t>
+          <t>1873335</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>543153</t>
+          <t>543846</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>626235</t>
+          <t>629041</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>580445</t>
+          <t>583503</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>670218</t>
+          <t>677694</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1149590</t>
+          <t>1153531</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1278501</t>
+          <t>1289580</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>174680</t>
+          <t>177656</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>232339</t>
+          <t>234715</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>255708</t>
+          <t>255772</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>323884</t>
+          <t>320247</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>449547</t>
+          <t>448058</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>537570</t>
+          <t>540516</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25258</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>50635</t>
+          <t>50557</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>49099</t>
+          <t>48286</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>81215</t>
+          <t>82695</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>80620</t>
+          <t>80904</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>122136</t>
+          <t>121642</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>337147</t>
+          <t>332228</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>387053</t>
+          <t>386915</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>291063</t>
+          <t>286789</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>343048</t>
+          <t>341041</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>638380</t>
+          <t>635999</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>716652</t>
+          <t>712006</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165645</t>
+          <t>162331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215849</t>
+          <t>210645</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>194707</t>
+          <t>194740</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245604</t>
+          <t>246357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>369602</t>
+          <t>372854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>443566</t>
+          <t>447229</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97457</t>
+          <t>99383</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138091</t>
+          <t>140133</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81165</t>
+          <t>82990</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120902</t>
+          <t>120286</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>189918</t>
+          <t>191045</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>246258</t>
+          <t>247977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39532</t>
+          <t>39800</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28798</t>
+          <t>29582</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53192</t>
+          <t>54793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54028</t>
+          <t>53521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86434</t>
+          <t>85690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11859</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31104</t>
+          <t>31072</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18807</t>
+          <t>18633</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39749</t>
+          <t>39743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>444414</t>
+          <t>445218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>509492</t>
+          <t>510856</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>395771</t>
+          <t>396105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>463307</t>
+          <t>462838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>863596</t>
+          <t>860533</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>954528</t>
+          <t>957631</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>250201</t>
+          <t>250127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309483</t>
+          <t>308350</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>290905</t>
+          <t>290299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>354898</t>
+          <t>353293</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>559999</t>
+          <t>557432</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644133</t>
+          <t>640959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>173494</t>
+          <t>173522</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>227000</t>
+          <t>229565</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182145</t>
+          <t>182938</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>238159</t>
+          <t>236608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>373814</t>
+          <t>373550</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>448946</t>
+          <t>449312</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36225</t>
+          <t>35811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65901</t>
+          <t>66439</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42704</t>
+          <t>41619</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72721</t>
+          <t>71039</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84501</t>
+          <t>83934</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127307</t>
+          <t>126129</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17573</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8798</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24167</t>
+          <t>25421</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15914</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36115</t>
+          <t>35978</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>328304</t>
+          <t>327074</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>388626</t>
+          <t>386457</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>329766</t>
+          <t>328632</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>385399</t>
+          <t>384633</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>675836</t>
+          <t>674097</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>754904</t>
+          <t>757752</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,52%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161274</t>
+          <t>161413</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>212547</t>
+          <t>209691</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178750</t>
+          <t>179373</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>232345</t>
+          <t>230671</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>355533</t>
+          <t>352321</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424611</t>
+          <t>424365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>130919</t>
+          <t>134327</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180010</t>
+          <t>181573</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>125212</t>
+          <t>126413</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>172993</t>
+          <t>169842</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>268462</t>
+          <t>272710</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>336176</t>
+          <t>341660</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27882</t>
+          <t>28528</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53861</t>
+          <t>56046</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33928</t>
+          <t>33497</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61358</t>
+          <t>61930</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68999</t>
+          <t>68638</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106939</t>
+          <t>105813</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>25555</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12144</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31188</t>
+          <t>31542</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50038</t>
+          <t>49108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>385489</t>
+          <t>386740</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>449206</t>
+          <t>447148</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>394434</t>
+          <t>395398</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>459692</t>
+          <t>459288</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>800587</t>
+          <t>801371</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>887552</t>
+          <t>892815</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,91%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>294851</t>
+          <t>295665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>356505</t>
+          <t>355476</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>321913</t>
+          <t>325375</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386483</t>
+          <t>384407</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>642636</t>
+          <t>636407</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>727649</t>
+          <t>725892</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121449</t>
+          <t>121742</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>168175</t>
+          <t>167341</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>161599</t>
+          <t>160596</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>211413</t>
+          <t>211125</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>295080</t>
+          <t>294308</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>359790</t>
+          <t>360680</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30286</t>
+          <t>30062</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55630</t>
+          <t>55345</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31853</t>
+          <t>30835</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58770</t>
+          <t>59181</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68088</t>
+          <t>66588</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>105817</t>
+          <t>105064</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25483</t>
+          <t>24889</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24178</t>
+          <t>23626</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48431</t>
+          <t>49149</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37392</t>
+          <t>36194</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>65699</t>
+          <t>66364</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1559329</t>
+          <t>1555355</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1683584</t>
+          <t>1676109</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1472178</t>
+          <t>1469090</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1587016</t>
+          <t>1593808</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3052310</t>
+          <t>3058728</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3230096</t>
+          <t>3220972</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>928383</t>
+          <t>929391</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1032602</t>
+          <t>1038096</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1043843</t>
+          <t>1044950</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1154173</t>
+          <t>1156814</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1990345</t>
+          <t>1999523</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2154909</t>
+          <t>2156440</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>567785</t>
+          <t>572158</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>662600</t>
+          <t>659602</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>595507</t>
+          <t>593025</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>688294</t>
+          <t>689918</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1192255</t>
+          <t>1193521</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1319142</t>
+          <t>1321516</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>134760</t>
+          <t>134815</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>185508</t>
+          <t>186464</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>158204</t>
+          <t>161558</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>212346</t>
+          <t>216966</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>306220</t>
+          <t>310837</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>380875</t>
+          <t>384445</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33574</t>
+          <t>33723</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>63718</t>
+          <t>63415</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>72091</t>
+          <t>71327</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>110997</t>
+          <t>110299</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>113099</t>
+          <t>112457</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>164374</t>
+          <t>164843</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>275442</t>
+          <t>275662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>329729</t>
+          <t>327139</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>230234</t>
+          <t>226846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>278761</t>
+          <t>277292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>519732</t>
+          <t>519490</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>590675</t>
+          <t>589982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,91%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>151422</t>
+          <t>151350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>196974</t>
+          <t>195613</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185017</t>
+          <t>182643</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234585</t>
+          <t>230368</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>350137</t>
+          <t>348039</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415157</t>
+          <t>417068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>115143</t>
+          <t>114899</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>158769</t>
+          <t>157638</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113980</t>
+          <t>114711</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156113</t>
+          <t>157746</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>240586</t>
+          <t>241056</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>302638</t>
+          <t>300173</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40117</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68221</t>
+          <t>67472</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40558</t>
+          <t>43100</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68831</t>
+          <t>69371</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89181</t>
+          <t>90329</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130678</t>
+          <t>131055</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19536</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28816</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20285</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42497</t>
+          <t>42084</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>412802</t>
+          <t>415815</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>481510</t>
+          <t>479239</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>397829</t>
+          <t>400595</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>464155</t>
+          <t>462682</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>830768</t>
+          <t>832894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>925298</t>
+          <t>923139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,74%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>253040</t>
+          <t>252955</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311472</t>
+          <t>310621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>256150</t>
+          <t>258851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>318666</t>
+          <t>317186</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>527624</t>
+          <t>529848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>610711</t>
+          <t>614992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>185185</t>
+          <t>183503</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>237715</t>
+          <t>236652</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>198132</t>
+          <t>195685</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>251139</t>
+          <t>249371</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>394293</t>
+          <t>395558</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>470114</t>
+          <t>471442</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44534</t>
+          <t>46216</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75419</t>
+          <t>77221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63730</t>
+          <t>64450</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98794</t>
+          <t>100024</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115979</t>
+          <t>116653</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164117</t>
+          <t>163954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>15783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36725</t>
+          <t>36030</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34264</t>
+          <t>32352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33592</t>
+          <t>34846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62449</t>
+          <t>62206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>232191</t>
+          <t>231213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>285953</t>
+          <t>285056</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>251281</t>
+          <t>253066</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>306324</t>
+          <t>306927</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>498972</t>
+          <t>501312</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>570682</t>
+          <t>576468</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203508</t>
+          <t>201395</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>256408</t>
+          <t>253940</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198024</t>
+          <t>197227</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>249593</t>
+          <t>248022</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417979</t>
+          <t>419039</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>489494</t>
+          <t>488132</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>177818</t>
+          <t>177582</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>227221</t>
+          <t>227729</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>169561</t>
+          <t>168273</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>220835</t>
+          <t>218464</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>361269</t>
+          <t>355725</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>431069</t>
+          <t>428661</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30480</t>
+          <t>31263</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56746</t>
+          <t>57318</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50746</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82713</t>
+          <t>84070</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89283</t>
+          <t>89003</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130454</t>
+          <t>131311</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37106</t>
+          <t>38465</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30148</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34378</t>
+          <t>33128</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62767</t>
+          <t>60574</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>372439</t>
+          <t>370512</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>433256</t>
+          <t>431412</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>434300</t>
+          <t>436479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>502218</t>
+          <t>500885</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>826466</t>
+          <t>829133</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>919162</t>
+          <t>920663</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255912</t>
+          <t>259000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>315307</t>
+          <t>316580</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>285701</t>
+          <t>285534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>351631</t>
+          <t>344036</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>562484</t>
+          <t>555345</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>641804</t>
+          <t>642257</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>153323</t>
+          <t>151865</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>199929</t>
+          <t>198918</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>139660</t>
+          <t>143900</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>190751</t>
+          <t>193607</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>306269</t>
+          <t>305673</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>378429</t>
+          <t>376755</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42437</t>
+          <t>40942</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>71029</t>
+          <t>70723</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52645</t>
+          <t>52809</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87483</t>
+          <t>87924</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102557</t>
+          <t>102599</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>146377</t>
+          <t>146945</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22381</t>
+          <t>22653</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>14380</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35433</t>
+          <t>36893</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>51638</t>
+          <t>49722</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1349411</t>
+          <t>1345062</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1470011</t>
+          <t>1465678</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1374481</t>
+          <t>1369363</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1494620</t>
+          <t>1492293</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2757405</t>
+          <t>2747031</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2917580</t>
+          <t>2922117</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>916647</t>
+          <t>921369</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1023124</t>
+          <t>1030236</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>975117</t>
+          <t>980211</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1086022</t>
+          <t>1095586</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1927644</t>
+          <t>1926754</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2089242</t>
+          <t>2079742</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>670098</t>
+          <t>671277</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>766896</t>
+          <t>766368</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>672026</t>
+          <t>673003</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>773456</t>
+          <t>768344</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1373793</t>
+          <t>1366150</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1507132</t>
+          <t>1509382</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>183791</t>
+          <t>180816</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>240852</t>
+          <t>239352</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>236983</t>
+          <t>238138</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>300976</t>
+          <t>301566</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>437149</t>
+          <t>434271</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>523237</t>
+          <t>520530</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>58716</t>
+          <t>59472</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>91583</t>
+          <t>94440</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>67172</t>
+          <t>67670</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>105556</t>
+          <t>106348</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>133624</t>
+          <t>134819</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>186605</t>
+          <t>184704</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>365574</t>
+          <t>387556</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>338602</t>
+          <t>361455</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>390445</t>
+          <t>413791</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>349724</t>
+          <t>377536</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>329027</t>
+          <t>355090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>370274</t>
+          <t>399896</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>715298</t>
+          <t>765092</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>680233</t>
+          <t>730475</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>747759</t>
+          <t>803337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>162116</t>
+          <t>182068</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139311</t>
+          <t>160022</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>183419</t>
+          <t>205684</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>195375</t>
+          <t>213560</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177805</t>
+          <t>195191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>212843</t>
+          <t>235289</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>357491</t>
+          <t>395628</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>327420</t>
+          <t>362238</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>386261</t>
+          <t>424473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68953</t>
+          <t>76790</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55481</t>
+          <t>61258</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85299</t>
+          <t>95302</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90302</t>
+          <t>95789</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78342</t>
+          <t>82666</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103760</t>
+          <t>112740</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>159255</t>
+          <t>172579</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>140345</t>
+          <t>152998</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>180866</t>
+          <t>194916</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22580</t>
+          <t>25791</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15090</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32284</t>
+          <t>36415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26858</t>
+          <t>30369</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>23527</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35446</t>
+          <t>40107</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>49438</t>
+          <t>56160</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39614</t>
+          <t>44602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60527</t>
+          <t>69037</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13521</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>23937</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>18706</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>23329</t>
+          <t>27528</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16805</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32036</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>632745</t>
+          <t>687823</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>632745</t>
+          <t>687823</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>632745</t>
+          <t>687823</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>672066</t>
+          <t>729164</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>672066</t>
+          <t>729164</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>672066</t>
+          <t>729164</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1304811</t>
+          <t>1416987</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1304811</t>
+          <t>1416987</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1304811</t>
+          <t>1416987</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>730816</t>
+          <t>523664</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>598990</t>
+          <t>486925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>927839</t>
+          <t>559070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>452521</t>
+          <t>494802</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>426126</t>
+          <t>465778</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>479069</t>
+          <t>525996</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1183336</t>
+          <t>1018466</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1043072</t>
+          <t>971301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1504441</t>
+          <t>1066020</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>50,57%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>302584</t>
+          <t>340871</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153328</t>
+          <t>306057</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>392146</t>
+          <t>377450</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>311147</t>
+          <t>354421</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>287545</t>
+          <t>327899</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335472</t>
+          <t>380396</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>613731</t>
+          <t>695292</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>401594</t>
+          <t>652589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>707056</t>
+          <t>738680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94567</t>
+          <t>111587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48345</t>
+          <t>91165</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126138</t>
+          <t>134997</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>114119</t>
+          <t>126705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100011</t>
+          <t>109513</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131125</t>
+          <t>142978</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>208686</t>
+          <t>238291</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>135610</t>
+          <t>210679</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>246603</t>
+          <t>263967</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43503</t>
+          <t>49386</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22385</t>
+          <t>35924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64478</t>
+          <t>67793</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56825</t>
+          <t>65975</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45324</t>
+          <t>53093</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71615</t>
+          <t>83129</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>100328</t>
+          <t>115361</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68586</t>
+          <t>95619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125662</t>
+          <t>139425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15799</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>10593</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26486</t>
+          <t>27593</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18836</t>
+          <t>23014</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12930</t>
+          <t>16004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26747</t>
+          <t>33222</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>34635</t>
+          <t>40619</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>31581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47336</t>
+          <t>53176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1187269</t>
+          <t>1043113</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1187269</t>
+          <t>1043113</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1187269</t>
+          <t>1043113</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>953448</t>
+          <t>1064916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>953448</t>
+          <t>1064916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>953448</t>
+          <t>1064916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2140716</t>
+          <t>2108029</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2140716</t>
+          <t>2108029</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2140716</t>
+          <t>2108029</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>349057</t>
+          <t>383458</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>318949</t>
+          <t>350484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>381865</t>
+          <t>417659</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>363595</t>
+          <t>385382</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>188844</t>
+          <t>359012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>481038</t>
+          <t>413930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>712652</t>
+          <t>768840</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>461102</t>
+          <t>732021</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>837246</t>
+          <t>812197</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>240316</t>
+          <t>273881</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>210408</t>
+          <t>243478</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>270993</t>
+          <t>306696</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>440200</t>
+          <t>275679</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>289976</t>
+          <t>250916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>670626</t>
+          <t>300839</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>680515</t>
+          <t>549561</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>524351</t>
+          <t>509647</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1030766</t>
+          <t>588210</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>80475</t>
+          <t>103065</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63660</t>
+          <t>82078</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101737</t>
+          <t>126803</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>82658</t>
+          <t>94859</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42707</t>
+          <t>80207</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>116519</t>
+          <t>112581</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>163133</t>
+          <t>197924</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>104426</t>
+          <t>170717</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>201570</t>
+          <t>227204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20789</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30468</t>
+          <t>35753</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33554</t>
+          <t>38283</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16576</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48892</t>
+          <t>50316</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>54343</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35215</t>
+          <t>48986</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69455</t>
+          <t>80210</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>16993</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>30526</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37130</t>
+          <t>46764</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>930837</t>
+          <t>808707</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>930837</t>
+          <t>808707</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>930837</t>
+          <t>808707</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1635353</t>
+          <t>1610602</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1635353</t>
+          <t>1610602</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1635353</t>
+          <t>1610602</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>469734</t>
+          <t>494054</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>437071</t>
+          <t>459852</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>502919</t>
+          <t>527931</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>578177</t>
+          <t>551351</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>532961</t>
+          <t>522069</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>684699</t>
+          <t>581804</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1047912</t>
+          <t>1045405</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>994736</t>
+          <t>1001889</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1165806</t>
+          <t>1091369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>51,96%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>257933</t>
+          <t>283262</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232991</t>
+          <t>256223</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>288377</t>
+          <t>313837</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>279322</t>
+          <t>305778</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>224604</t>
+          <t>281009</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>310170</t>
+          <t>331826</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>537256</t>
+          <t>589040</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>472672</t>
+          <t>545865</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>579247</t>
+          <t>625495</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>119270</t>
+          <t>126516</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99861</t>
+          <t>106381</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>141188</t>
+          <t>147320</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>133774</t>
+          <t>142935</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>105083</t>
+          <t>125488</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156331</t>
+          <t>165659</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>253045</t>
+          <t>269450</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>218915</t>
+          <t>239670</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>284529</t>
+          <t>298633</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -14039,67 +14039,67 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>49273</t>
+          <t>53582</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37302</t>
+          <t>40570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65427</t>
+          <t>69515</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>78792</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>64779</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>95474</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>7,08%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>72132</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>56218</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>88457</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>121405</t>
+          <t>132374</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102465</t>
+          <t>112251</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143014</t>
+          <t>153530</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>28070</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39974</t>
+          <t>42563</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>26557</t>
+          <t>34223</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19522</t>
+          <t>25121</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35326</t>
+          <t>43837</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>54627</t>
+          <t>64182</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>42174</t>
+          <t>50685</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>69352</t>
+          <t>79714</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>924281</t>
+          <t>987372</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>924281</t>
+          <t>987372</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>924281</t>
+          <t>987372</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1089962</t>
+          <t>1113079</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1089962</t>
+          <t>1113079</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1089962</t>
+          <t>1113079</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2014244</t>
+          <t>2100451</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2014244</t>
+          <t>2100451</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2014244</t>
+          <t>2100451</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1915182</t>
+          <t>1788731</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1777086</t>
+          <t>1722732</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2238237</t>
+          <t>1855514</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1744016</t>
+          <t>1809071</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1343495</t>
+          <t>1754612</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1882755</t>
+          <t>1864773</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3659198</t>
+          <t>3597802</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3378310</t>
+          <t>3510424</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3989599</t>
+          <t>3689503</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>962949</t>
+          <t>1080083</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>761979</t>
+          <t>1021459</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1057465</t>
+          <t>1141295</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1226044</t>
+          <t>1149437</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1060302</t>
+          <t>1094853</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1822493</t>
+          <t>1196694</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2188993</t>
+          <t>2229520</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1988893</t>
+          <t>2162752</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2621105</t>
+          <t>2314886</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>363266</t>
+          <t>417958</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>289046</t>
+          <t>380728</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>410964</t>
+          <t>460780</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>420852</t>
+          <t>460287</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>339331</t>
+          <t>425025</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>465736</t>
+          <t>494231</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>784118</t>
+          <t>878245</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>666341</t>
+          <t>822686</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>859817</t>
+          <t>936556</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>136144</t>
+          <t>153256</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>104626</t>
+          <t>130008</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>165982</t>
+          <t>180450</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>189369</t>
+          <t>213419</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>150533</t>
+          <t>190321</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>218401</t>
+          <t>242871</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>325513</t>
+          <t>366675</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>280962</t>
+          <t>336106</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>365605</t>
+          <t>408618</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>71269</t>
+          <t>80175</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>53845</t>
+          <t>62733</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>91305</t>
+          <t>98883</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>66032</t>
+          <t>83651</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>52190</t>
+          <t>69460</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>79589</t>
+          <t>101386</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>137302</t>
+          <t>163826</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>115044</t>
+          <t>140389</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>161177</t>
+          <t>187969</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3448811</t>
+          <t>3520203</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3448811</t>
+          <t>3520203</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3448811</t>
+          <t>3520203</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3646313</t>
+          <t>3715865</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3646313</t>
+          <t>3715865</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3646313</t>
+          <t>3715865</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7095124</t>
+          <t>7236068</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7095124</t>
+          <t>7236068</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7095124</t>
+          <t>7236068</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
